--- a/results/breakdown/2050/nitrous oxide production, AON 100, fossil ammonia.xlsx
+++ b/results/breakdown/2050/nitrous oxide production, AON 100, fossil ammonia.xlsx
@@ -426,7 +426,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>2.629386791636014</v>
+        <v>2.66364887068573</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -443,7 +443,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>2.631710717656714</v>
+        <v>2.662956748435941</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -460,7 +460,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>0.0003602590578176867</v>
+        <v>0.0003975910233074946</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -477,7 +477,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>-0.002556973159987019</v>
+        <v>0.0002804890212159799</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -494,7 +494,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>-0.0001271577008650675</v>
+        <v>1.394865570718024E-05</v>
       </c>
       <c r="E6">
         <v>1</v>

--- a/results/breakdown/2050/nitrous oxide production, AON 100, fossil ammonia.xlsx
+++ b/results/breakdown/2050/nitrous oxide production, AON 100, fossil ammonia.xlsx
@@ -426,7 +426,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>2.66364887068573</v>
+        <v>2.663648870685731</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -443,7 +443,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>2.662956748435941</v>
+        <v>2.662956748435942</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -460,7 +460,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>0.0003975910233074946</v>
+        <v>0.000397591023307495</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -477,7 +477,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>0.0002804890212159799</v>
+        <v>0.0002804890212159755</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -494,7 +494,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>1.394865570718024E-05</v>
+        <v>1.394865570717995E-05</v>
       </c>
       <c r="E6">
         <v>1</v>

--- a/results/breakdown/2050/nitrous oxide production, AON 100, fossil ammonia.xlsx
+++ b/results/breakdown/2050/nitrous oxide production, AON 100, fossil ammonia.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\results\breakdown\2050\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09CFD6D-F479-4EC9-90F6-C6F983DBBB03}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -46,8 +52,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -110,6 +116,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -156,7 +170,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -188,9 +202,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -222,6 +254,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -397,11 +447,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="68.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -415,7 +468,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>4</v>
       </c>
@@ -426,13 +479,13 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>2.663648870685731</v>
+        <v>2.6636488706857309</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>0</v>
       </c>
@@ -449,7 +502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -460,13 +513,13 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>0.000397591023307495</v>
+        <v>3.9759102330749502E-4</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -477,13 +530,13 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>0.0002804890212159755</v>
+        <v>2.8048902121597551E-4</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -494,10 +547,14 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>1.394865570717995E-05</v>
+        <v>1.394865570717995E-5</v>
       </c>
       <c r="E6">
         <v>1</v>
+      </c>
+      <c r="F6">
+        <f>D4+D6</f>
+        <v>4.1153967901467499E-4</v>
       </c>
     </row>
   </sheetData>
